--- a/data/trans_dic/P25C$pormicuenta_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P25C$pormicuenta_2023-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue sin ayuda específica</t>
+          <t>Población cuyo método para dejar de fumar fue sin ayuda específica (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>87,65; 100,0</t>
+          <t>90,49; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>92,3; 100,0</t>
+          <t>92,13; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>90,55; 100,0</t>
+          <t>87,07; 99,9</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>70,56; 86,79</t>
+          <t>71,49; 87,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>81,27; 94,32</t>
+          <t>80,83; 94,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>76,71; 88,71</t>
+          <t>77,2; 88,35</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>85,94; 98,6</t>
+          <t>86,78; 98,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>81,85; 95,41</t>
+          <t>82,25; 95,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>87,19; 95,93</t>
+          <t>87,16; 96,02</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>69,69; 88,56</t>
+          <t>71,34; 88,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>82,11; 94,25</t>
+          <t>81,82; 94,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77,13; 89,05</t>
+          <t>77,73; 88,94</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>92,94; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>79,97; 100,0</t>
+          <t>79,33; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89,88; 100,0</t>
+          <t>90,25; 100,0</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>89,11; 98,91</t>
+          <t>89,42; 98,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>90,95; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>91,14; 99,13</t>
+          <t>91,24; 99,21</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>89,39; 97,52</t>
+          <t>89,35; 97,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>82,78; 93,28</t>
+          <t>82,12; 93,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88,19; 94,74</t>
+          <t>88,41; 94,7</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>88,57; 99,55</t>
+          <t>88,82; 99,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>80,29; 96,64</t>
+          <t>80,42; 96,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>89,24; 99,37</t>
+          <t>89,2; 99,43</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>88,68; 97,0</t>
+          <t>88,66; 97,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>87,33; 92,45</t>
+          <t>87,16; 92,32</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>89,13; 95,92</t>
+          <t>89,04; 95,7</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue sin ayuda específica</t>
+          <t>Población cuyo método para dejar de fumar fue sin ayuda específica (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>41678; 47549</t>
+          <t>43029; 47549</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11157; 12088</t>
+          <t>11137; 12088</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>54002; 59637</t>
+          <t>51927; 59574</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>77979; 95920</t>
+          <t>79009; 96902</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>53193; 61730</t>
+          <t>52904; 61774</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>134984; 156092</t>
+          <t>135851; 155472</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>59084; 67788</t>
+          <t>59660; 67709</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>40513; 47224</t>
+          <t>40710; 47488</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>103100; 113425</t>
+          <t>103057; 113535</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>65835; 83670</t>
+          <t>67395; 83238</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>47779; 54842</t>
+          <t>47609; 54839</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>117752; 135941</t>
+          <t>118667; 135777</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13767; 14812</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6658; 8326</t>
+          <t>6605; 8326</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20797; 23138</t>
+          <t>20882; 23138</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>40440; 44886</t>
+          <t>40582; 44847</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10027; 11024</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>51406; 55913</t>
+          <t>51467; 55958</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>108894; 118798</t>
+          <t>108849; 118480</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>78500; 88449</t>
+          <t>77870; 88753</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>191066; 205248</t>
+          <t>191541; 205160</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>306670; 344683</t>
+          <t>307525; 344798</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>30547; 36769</t>
+          <t>30598; 36724</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>342928; 381872</t>
+          <t>342777; 382121</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>753362; 824064</t>
+          <t>753183; 824349</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>294702; 311951</t>
+          <t>294116; 311532</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1058013; 1138617</t>
+          <t>1056936; 1136007</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25C$pormicuenta_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P25C$pormicuenta_2023-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,74%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>90,49; 100,0</t>
+          <t>91,22; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>92,13; 100,0</t>
+          <t>78,24; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87,07; 99,9</t>
+          <t>91,88; 100,0</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>82,49%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>71,49; 87,68</t>
+          <t>69,55; 85,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>80,83; 94,39</t>
+          <t>81,0; 94,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77,2; 88,35</t>
+          <t>76,76; 87,88</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,61%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>86,78; 98,49</t>
+          <t>86,35; 98,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>82,25; 95,94</t>
+          <t>81,58; 95,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>87,16; 96,02</t>
+          <t>87,03; 95,77</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>85,08%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>71,34; 88,11</t>
+          <t>72,68; 89,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>81,82; 94,24</t>
+          <t>82,95; 94,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77,73; 88,94</t>
+          <t>78,9; 89,68</t>
         </is>
       </c>
     </row>
@@ -754,12 +754,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>79,33; 100,0</t>
+          <t>75,8; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>90,25; 100,0</t>
+          <t>93,08; 100,0</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,41%</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>89,42; 98,82</t>
+          <t>89,76; 98,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>91,24; 99,21</t>
+          <t>90,71; 98,91</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,14%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>89,35; 97,26</t>
+          <t>89,95; 97,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>82,12; 93,6</t>
+          <t>82,49; 93,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88,41; 94,7</t>
+          <t>88,83; 94,7</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>90,53%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>88,82; 99,58</t>
+          <t>84,47; 94,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>80,42; 96,52</t>
+          <t>81,68; 95,85</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>89,2; 99,43</t>
+          <t>85,44; 93,78</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>89,74%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>88,66; 97,03</t>
+          <t>86,52; 91,71</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>87,16; 92,32</t>
+          <t>87,7; 92,76</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>89,04; 95,7</t>
+          <t>87,84; 91,47</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>46546</t>
+          <t>49496</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11922</t>
+          <t>11882</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58468</t>
+          <t>61378</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>43029; 47549</t>
+          <t>45937; 50361</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11137; 12088</t>
+          <t>9731; 12436</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51927; 59574</t>
+          <t>57698; 62797</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>88242</t>
+          <t>93165</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>58402</t>
+          <t>59727</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>146645</t>
+          <t>152892</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>79009; 96902</t>
+          <t>82485; 101214</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>52904; 61774</t>
+          <t>54061; 63192</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>135851; 155472</t>
+          <t>142276; 162888</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>64932</t>
+          <t>64020</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44544</t>
+          <t>44635</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>109475</t>
+          <t>108655</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>59660; 67709</t>
+          <t>58447; 66470</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>40710; 47488</t>
+          <t>40492; 47239</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>103057; 113535</t>
+          <t>102108; 112358</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>76690</t>
+          <t>88229</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>51926</t>
+          <t>58551</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>128615</t>
+          <t>146780</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>67395; 83238</t>
+          <t>78085; 96068</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>47609; 54839</t>
+          <t>53993; 61540</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>118667; 135777</t>
+          <t>136130; 154727</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14812</t>
+          <t>15697</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7949</t>
+          <t>8443</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22761</t>
+          <t>24140</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6605; 8326</t>
+          <t>6695; 8832</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20882; 23138</t>
+          <t>22831; 24529</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>43365</t>
+          <t>42526</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>11024</t>
+          <t>11500</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>54389</t>
+          <t>54026</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>40582; 44847</t>
+          <t>39976; 44034</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>51467; 55958</t>
+          <t>50831; 55424</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>115049</t>
+          <t>134740</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>84118</t>
+          <t>95407</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>199166</t>
+          <t>230147</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>108849; 118480</t>
+          <t>128057; 139026</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>77870; 88753</t>
+          <t>88603; 100140</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>191541; 205160</t>
+          <t>221864; 236534</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>336401</t>
+          <t>102782</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>34312</t>
+          <t>40056</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>370712</t>
+          <t>142838</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>307525; 344798</t>
+          <t>95906; 107377</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>30598; 36724</t>
+          <t>36134; 42406</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>342777; 382121</t>
+          <t>134807; 147971</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>786038</t>
+          <t>590654</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>304194</t>
+          <t>330202</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1090232</t>
+          <t>920856</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>753183; 824349</t>
+          <t>571253; 605462</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>294116; 311532</t>
+          <t>320890; 339402</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1056936; 1136007</t>
+          <t>901378; 938614</t>
         </is>
       </c>
     </row>
